--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>10.81325674057007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3986,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>8.150836944580078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4015,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>9.888144493103027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4044,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>7.138302326202393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4073,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>58.83424758911133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4102,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>8.557939291000366</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>4.19315242767334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>6.435263156890869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4189,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>9.027895927429199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>3.653733015060425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>10.00926089286804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>6.066638469696045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>6.120968818664551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>12.15586256980896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>4.692219734191895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>4.768797874450684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4421,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>3.842477560043335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>11.54637694358826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>11.79169178009033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4508,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>14.97159242630005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4537,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>8.130645513534546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>5.700356006622314</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>14.88777089118958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>9.783795595169067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>5.18953013420105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>4.015435218811035</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4711,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>5.685373544692993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>3.097601175308228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4769,7 +4769,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>8.99478554725647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4798,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>4.854998111724854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>4.993186712265015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4856,7 +4856,7 @@
         <v>0</v>
       </c>
       <c r="I33">
-        <v>4.996589422225952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4885,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>10.03497385978699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4914,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="I35">
-        <v>3.928797483444214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>4.746701240539551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4972,7 +4972,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>6.511656761169434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -5001,7 +5001,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>3.277551651000977</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>5.241531610488892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>4.389701366424561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -5088,7 +5088,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>4.000663042068481</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>13.35368967056274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -5146,7 +5146,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>4.707056045532227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -5175,7 +5175,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>9.233188152313232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="I45">
-        <v>3.970499277114868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5233,7 +5233,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>20.13505625724792</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5262,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="I47">
-        <v>4.443522691726685</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="I48">
-        <v>9.36880087852478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5320,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>7.990288257598877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5349,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>6.228190898895264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>4.427495241165161</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -5407,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>5.483512401580811</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>8.915542602539062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5465,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>114.4735369682312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5494,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>5.038863182067871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5523,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>4.320052862167358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5552,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>5.918801546096802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>10.02957129478455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>8.272061824798584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5639,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>8.874599933624268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>12.04272747039795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>5.909388780593872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5726,7 +5726,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>4.63789439201355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>4.446598768234253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>14.2784481048584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>6.753361463546753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5842,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>4.840214252471924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>6.913538694381714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5900,7 +5900,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>3.62354588508606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>4.182940244674683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5958,7 +5958,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>14.21262168884277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5987,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>3.748235464096069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>8.09022045135498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -6045,7 +6045,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>15.97316431999207</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -6074,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>9.33722972869873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -6103,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>6.038492441177368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>3.771779775619507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -6161,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>5.440913915634155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -6190,7 +6190,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>10.13884687423706</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>5.10435152053833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>17.09147119522095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>5.940203189849854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -6306,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>12.657386302948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -6335,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>23.08734369277954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="I85">
-        <v>4.502096891403198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>42.08172130584717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -6422,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>11.97855997085571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="I88">
-        <v>5.95652961730957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6480,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <v>4.297468662261963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>8.609579563140869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6538,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="I91">
-        <v>4.857425212860107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6567,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>22.10258197784424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6596,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>3.674275398254395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>5.247590780258179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6654,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>13.14393639564514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6683,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>4.225426912307739</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>4.000383138656616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6741,7 +6741,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>6.372577905654907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6770,7 +6770,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>5.727467060089111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>20.61308217048645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6828,7 +6828,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>6.21635103225708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6857,7 +6857,7 @@
         <v>0</v>
       </c>
       <c r="I102">
-        <v>4.779575347900391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6886,7 +6886,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>6.186205863952637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6915,7 +6915,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>10.28345251083374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>4.793151378631592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6973,7 +6973,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>3.236098051071167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -7002,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>8.99904727935791</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>44.95155882835388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -7060,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="I109">
-        <v>62.71422338485718</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -7089,7 +7089,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>9.871891021728516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -7118,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="I111">
-        <v>6.408597946166992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -7147,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="I112">
-        <v>5.852559089660645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -7176,7 +7176,7 @@
         <v>0</v>
       </c>
       <c r="I113">
-        <v>6.139110565185547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>45.63692331314087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -7234,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>41.24123382568359</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>20.1698169708252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -7292,7 +7292,7 @@
         <v>1</v>
       </c>
       <c r="I117">
-        <v>9.329542636871338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -7321,7 +7321,7 @@
         <v>1</v>
       </c>
       <c r="I118">
-        <v>3.60384726524353</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="I119">
-        <v>8.777697324752808</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -7379,7 +7379,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>5.281746387481689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -7408,7 +7408,7 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>5.60248875617981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -7437,7 +7437,7 @@
         <v>1</v>
       </c>
       <c r="I122">
-        <v>6.362384796142578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="I123">
-        <v>5.427461624145508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7492,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="I124">
-        <v>6.762035131454468</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7521,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="I125">
-        <v>6.486087083816528</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="I126">
-        <v>7.143629789352417</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7579,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>5.072003841400146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>1.616013050079346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>5.651674747467041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>6.914240598678589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7692,7 +7692,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>5.90988826751709</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="I132">
-        <v>8.798473596572876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7750,7 +7750,7 @@
         <v>0</v>
       </c>
       <c r="I133">
-        <v>9.892954349517822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7779,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="I134">
-        <v>7.888590574264526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7808,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>6.056259870529175</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7837,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="I136">
-        <v>8.850624322891235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7866,7 +7866,7 @@
         <v>1</v>
       </c>
       <c r="I137">
-        <v>6.611752271652222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7895,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="I138">
-        <v>6.808372020721436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7924,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="I139">
-        <v>8.295631170272827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7953,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="I140">
-        <v>13.3153829574585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7982,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="I141">
-        <v>5.957265615463257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="I142">
-        <v>10.56917381286621</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -8040,7 +8040,7 @@
         <v>1</v>
       </c>
       <c r="I143">
-        <v>36.12386155128479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -8069,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="I144">
-        <v>5.662687063217163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="I145">
-        <v>4.69596529006958</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -8127,7 +8127,7 @@
         <v>0</v>
       </c>
       <c r="I146">
-        <v>2.610730171203613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -8156,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="I147">
-        <v>14.35012626647949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -8185,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="I148">
-        <v>6.787137746810913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -8214,7 +8214,7 @@
         <v>1</v>
       </c>
       <c r="I149">
-        <v>9.357023000717163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="I150">
-        <v>3.080440759658813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -8269,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="I151">
-        <v>9.733180999755859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -8298,7 +8298,7 @@
         <v>0</v>
       </c>
       <c r="I152">
-        <v>9.478247165679932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -8327,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="I153">
-        <v>7.597188949584961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -8356,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="I154">
-        <v>23.95481038093567</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="I155">
-        <v>12.71105241775513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>6.165678977966309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -8443,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="I157">
-        <v>16.15507006645203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="I158">
-        <v>9.96678614616394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8501,7 +8501,7 @@
         <v>1</v>
       </c>
       <c r="I159">
-        <v>13.52166819572449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8530,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>8.948527097702026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8556,7 +8556,7 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <v>10.53068542480469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8585,7 +8585,7 @@
         <v>0</v>
       </c>
       <c r="I162">
-        <v>3.461826086044312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8614,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="I163">
-        <v>4.612885713577271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8643,7 +8643,7 @@
         <v>1</v>
       </c>
       <c r="I164">
-        <v>12.3976571559906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>13.09096050262451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8698,7 +8698,7 @@
         <v>0</v>
       </c>
       <c r="I166">
-        <v>16.57690763473511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="I167">
-        <v>22.12388157844543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8756,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="I168">
-        <v>6.43290376663208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -8785,7 +8785,7 @@
         <v>0</v>
       </c>
       <c r="I169">
-        <v>8.111245155334473</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -8814,7 +8814,7 @@
         <v>0</v>
       </c>
       <c r="I170">
-        <v>10.41349720954895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="I171">
-        <v>6.579582452774048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -8872,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="I172">
-        <v>5.314276695251465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -8901,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="I173">
-        <v>3.87591028213501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -8930,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="I174">
-        <v>17.44456720352173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -8959,7 +8959,7 @@
         <v>0</v>
       </c>
       <c r="I175">
-        <v>6.373293876647949</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="I176">
-        <v>9.500179052352905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -9017,7 +9017,7 @@
         <v>1</v>
       </c>
       <c r="I177">
-        <v>7.861098051071167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="I178">
-        <v>9.117769241333008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -9075,7 +9075,7 @@
         <v>0</v>
       </c>
       <c r="I179">
-        <v>6.635931491851807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -9104,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="I180">
-        <v>14.4714560508728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -9133,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="I181">
-        <v>7.864300489425659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -9162,7 +9162,7 @@
         <v>1</v>
       </c>
       <c r="I182">
-        <v>9.329308986663818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -9191,7 +9191,7 @@
         <v>1</v>
       </c>
       <c r="I183">
-        <v>16.37660336494446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -9220,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="I184">
-        <v>16.84522151947021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>22.9029393196106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -9278,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>7.876063108444214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -9307,7 +9307,7 @@
         <v>0</v>
       </c>
       <c r="I187">
-        <v>14.25455975532532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -9336,7 +9336,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>6.84443736076355</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -9365,7 +9365,7 @@
         <v>1</v>
       </c>
       <c r="I189">
-        <v>6.257341384887695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="I190">
-        <v>14.00530791282654</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -9423,7 +9423,7 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>6.559771299362183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -9452,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>8.648126125335693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
       <c r="I193">
-        <v>13.05357837677002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -9510,7 +9510,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>5.142669200897217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -9539,7 +9539,7 @@
         <v>1</v>
       </c>
       <c r="I195">
-        <v>8.162469387054443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="I196">
-        <v>6.464340209960938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -9594,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="I197">
-        <v>10.25891923904419</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -9623,7 +9623,7 @@
         <v>1</v>
       </c>
       <c r="I198">
-        <v>13.31890320777893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -9652,7 +9652,7 @@
         <v>0</v>
       </c>
       <c r="I199">
-        <v>13.79594135284424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -9681,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="I200">
-        <v>8.02793288230896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -9710,7 +9710,7 @@
         <v>1</v>
       </c>
       <c r="I201">
-        <v>9.145234823226929</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
+++ b/think3d_repro/outputs/run2/vlmeval_runs/SPAgent_4B_pi3x_spatial/VSIBench/SPAgent_4B_pi3x_spatial_VSIBench.xlsx
@@ -1997,7 +1997,26 @@
 &lt;answer&gt;(A) A. trash can&lt;/answer&gt;</t>
   </si>
   <si>
-    <t>&lt;answer&gt;(D) D. plant&lt;/answer&gt;</t>
+    <t>To determine which object (kettle, cutting board, refrigerator, plant) is closest to the sofa, we need to analyze the spatial relationships between these objects and the sofa based on the provided frames. The frames show a living room and kitchen area, with the sofa prominently visible in several frames.
+### Step 1: Identify the locations of the objects and the sofa
+From the frames, we can observe:
+- The **sofa** is located in the living room, near the center of the room in several frames.
+- The **plant** is visible in the dining area, near the dining table, and also on a shelf in the living room.
+- The **kettle** is located on the kitchen counter, near the stove.
+- The **cutting board** is visible on the kitchen counter, near the sink.
+- The **refrigerator** is not explicitly visible in the frames, but it is typically located in the kitchen area, near the counter and cabinets.
+### Step 2: Determine the relative distances from the sofa
+From the frames, we can infer the following:
+- The **plant** is located in the dining area, which is adjacent to the living room. The distance from the sofa to the plant is relatively close, as the plant is visible in the living room area.
+- The **kettle** and **cutting board** are located in the kitchen, which is adjacent to the living room. The distance from the sofa to these objects is also relatively close.
+- The **refrigerator** is typically located in the kitchen, near the counter. The distance from the sofa to the refrigerator is also relatively close.
+### Step 3: Compare the distances
+Based on the frames, the **plant** is located in the living room area, which is close to the sofa. The **kettle** and **cutting board** are located in the kitchen, which is adjacent to the living room. The **refrigerator** is also located in the kitchen, which is adjacent to the living room.
+### Step 4: Select the closest object
+The **plant** is located in the living room area, which is close to the sofa. The **kettle** and **cutting board** are located in the kitchen, which is adjacent to the living room. The **refrigerator** is also located in the kitchen, which is adjacent to the living room.
+### Final Answer
+The closest object to the sofa is the **plant**, as it is located in the living room area, which is close to the sofa.
+&lt;answer&gt;(D) D. plant&lt;/answer&gt;</t>
   </si>
   <si>
     <t>&lt;answer&gt;(D) D. table&lt;/answer&gt;</t>
@@ -6973,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>3.606074571609497</v>
       </c>
     </row>
     <row r="107" spans="1:9">
